--- a/catalog/catalog.xlsx
+++ b/catalog/catalog.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>同上。2026-10-21の検索で、委託調査一覧の受託者がマッキンゼーであることを確認</t>
         </is>
       </c>
     </row>
@@ -1536,6 +1536,368 @@
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>スイムレーン、時系列マトリクス、調査の土台</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MCK-2024-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>McKinsey（METI委託）</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>令和6年度 委託調査報告書（1000124、題名は一覧で確認）</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>経済産業省</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.meti.go.jp/meti_lib/report/2024FY/1000124.pdf</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>未取得</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>委託調査一覧（2024年度）でMCK-2024-01と並んで掲載。受託者と題名をPCで確認してから採否を決める</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RB-2021-01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Roland Berger（METI委託）</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>令和3年度製造基盤技術実態等調査（我が国製造業における技術分野の長期的展望に関する調査）</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>経済産業省</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.meti.go.jp/meti_lib/report/2021FY/000069.pdf</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>横型スライド（要確認）</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>未取得</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>表紙に受託者名の記載あり（検索結果で確認）。クラウド環境からはMETIに接続できない。PCから取得する</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ADL-2021-01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Arthur D. Little（内閣官房委託）</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>医薬品・再生医療等の産業化に関する調査 最終報告書の概要</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>内閣官房 健康・医療戦略室</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.kantei.go.jp/jp/singi/kenkouiryou/iyakuhin/dai3/sankou1.pdf</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>横型スライド（要確認）</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>未取得</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>会議の参考資料として公開された概要版。PCから取得する</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EY-2025-01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EY（METI委託）</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>令和6年度技術開発調査等の推進事業費（あるべきイノベーション政策の検討に向けた調査事業）</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>経済産業省</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.meti.go.jp/meti_lib/report/2024FY/000288.pdf</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>未取得</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>受託者はEY税理士法人。縦型の文章報告書なら対象外にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>METI-2025-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>（受託者要確認）</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>令和6年度エネルギー需給構造高度化対策調査等事業（中小企業の構造転換のための調査事業）最終報告書</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>経済産業省</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.meti.go.jp/meti_lib/report/2024FY/000514.pdf</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>未取得</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>受託者がコンサルティングファームか一覧で確認してから採否を決める</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>METI-2025-03</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>（受託者要確認）</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>令和6年度技術開発調査等の推進事業（イノベーション・エコシステム構築に当たっての人材・技術・設備の流動化についての調査）</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>経済産業省</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.meti.go.jp/meti_lib/report/2024FY/1000143.pdf</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>未取得</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ENECHO-2024-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>（発表者要確認）</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>基本政策分科会 プレゼンテーション「エネルギー・脱炭素化に対する民間企業の動向：グローバルな視点から」</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>資源エネルギー庁</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.enecho.meti.go.jp/committee/council/basic_policy_subcommittee/2024/057/057_007.pdf</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>横型スライド（要確認）</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>未取得</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>審議会でのファームの発表資料の可能性。発表者を表紙で確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>METI-LIST-2024</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>（各社）</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>経済産業省 委託調査報告書 一覧（2024年度）</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>経済産業省</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.meti.go.jp/meti_lib/report/2024FY/itakuichiran2024FY.pdf</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>一覧PDF</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>候補探し用</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>委託事業者名の列で、外資系ファーム（マッキンゼー、BCG、ベイン、ADL、ローランド・ベルガー、カーニー、アクセンチュア、デロイト、PwC、EY、KPMG）を探す</t>
         </is>
       </c>
     </row>
@@ -2707,12 +3069,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>新型候補</t>
+          <t>P57</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2762,12 +3124,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>新型候補</t>
+          <t>P56</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4577,7 +4939,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>新型候補</t>
+          <t>P59</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4852,7 +5214,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>新型候補</t>
+          <t>P58</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">

--- a/catalog/catalog.xlsx
+++ b/catalog/catalog.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1898,6 +1898,51 @@
       <c r="I32" t="inlineStr">
         <is>
           <t>委託事業者名の列で、外資系ファーム（マッキンゼー、BCG、ベイン、ADL、ローランド・ベルガー、カーニー、アクセンチュア、デロイト、PwC、EY、KPMG）を探す</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>JNB01</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Carnot AI（Jinba）</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>consulting-pptx-skill のパーツ集の印刷版（SlideCatalog_16x9.pdf、62型）</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>GitHub（MIT License）</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://github.com/carnot-tech/jinba-consulting-pptx-skill</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>横型スライド（型の見本帳）</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>取得済</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>コンサル会社の公開資料ではなく、AIでコンサル型スライドを作るスキルの見本帳。規約（references/slide-rules.md）を参考に rules/slide-rules.md のH章を追加し、不足していた7型をP72〜P78として追加（2026-10-22）。PDFはリポジトリに入れず、PCの参照ライブラリ/sources/に置く（git clone で取得できる）</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6410,6 +6455,517 @@
       <c r="O81" t="inlineStr">
         <is>
           <t>問題点と外部からの指摘を左右の枠に分け、見出しのアイコンで種類を示す</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>11</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>JNB01</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>11</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>P72</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>型名の題（見本帳）</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2・左右（1:3）</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>横棒</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>左の濃い塗りのパネルに番号と主張</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>出典行のみ</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>各論の左1/4に論点番号と主張を置き、一覧ページとの往復を作る。本リポジトリでは塗りの箱でなく紺の番号と縦線で区切った</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>16</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>JNB01</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>16</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>P74</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>型名の題（見本帳）</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>バブル行列</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>件数を円の大きさで</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>出典行のみ</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>行×段階の件数を円で並べ、どこに溜まっているかを一目で見せる</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>17</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>JNB01</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>17</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>P75</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>型名の題（見本帳）</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2・左右</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>多数の細い順位棒</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>上位の棒だけ濃色</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>区切りの注記</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>出典行のみ</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>数十〜数百の項目を名前なしの細い棒で並べ、裾の長さと上位の集中を見せる</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>20</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>JNB01</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>20</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>P78</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>型名の題（見本帳）</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>3・左中右</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>向きの違う矢羽</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>押し下げ側だけ濃色</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>出典行のみ</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>押し上げ要因と押し下げ要因を左右に並べ、中央の矢羽で向きを示す</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>23</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>JNB01</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>23</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>P73</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>型名の題（見本帳）</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2・左右</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>増減の縦棒</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>左に増減それぞれの合計を大きく</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>出典行のみ</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>基準線の上下に増える分と減る分を描き、差し引きだけでは見えない中身を示す</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>44</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>JNB01</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>44</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>P76</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>型名の題（見本帳）</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>入れ子の行列</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>大分類を塗りの箱で</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>出典行のみ</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>大分類の中に小分類の行を入れ子にする。本リポジトリでは大分類を縦線で括り、小計を添えた</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>51</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>JNB01</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>51</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>P77</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>型名の題（見本帳）</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1・3列</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>課題→原因→解決</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>矢印で3段をつなぐ</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>出典行のみ</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>課題と解決の間に原因を1段挟み、なぜその解決かを読ませる</t>
         </is>
       </c>
     </row>

--- a/catalog/catalog.xlsx
+++ b/catalog/catalog.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1943,6 +1943,186 @@
       <c r="I33" t="inlineStr">
         <is>
           <t>コンサル会社の公開資料ではなく、AIでコンサル型スライドを作るスキルの見本帳。規約（references/slide-rules.md）を参考に rules/slide-rules.md のH章を追加し、不足していた7型をP72〜P78として追加（2026-10-22）。PDFはリポジトリに入れず、PCの参照ライブラリ/sources/に置く（git clone で取得できる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>McKinsey（審議会発表）</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>日本の脱炭素化への道筋（グリーントランスフォーメーション推進小委員会 第5回 資料2-3）</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>経済産業省（産業構造審議会 GX推進小委員会、2022年3月23日）</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://www.meti.go.jp/shingikai/sankoshin/sangyo_gijutsu/green_transformation/005.html（資料2-3、005_02_03.pdf）</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>横型スライド（38p）</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>取得済</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-10-27 ユーザーがPCから添付。右3分の1の読み取り帯、行そろえの小図、コストカーブ、割合の丸の印の手本</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MCK05</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>McKinsey（検討会発表）</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>長期エネルギー貯蔵システム（LDES）を取り巻く市場環境（2024年度 第4回 定置用蓄電システム普及拡大検討会 資料4-2）</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>経済産業省（定置用蓄電システム普及拡大検討会、2024年11月11日）</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.meti.go.jp/shingikai/energy_environment/storage_system/pdf/2024_004_04_02.pdf</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>横型スライド（13p、濃紺の背景）</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>取得済</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-10-27 ユーザーがPCから添付。背景・配色は本リポジトリの規定と合わないため、配置だけを参考にした</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DTC-2022-01</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte（審議会発表）</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>脱炭素化に伴うエネルギー価格変化によるインパクト（GX推進小委員会 第5回 配布資料）</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>経済産業省（産業構造審議会 GX推進小委員会、2022年3月23日）</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.meti.go.jp/shingikai/sankoshin/sangyo_gijutsu/green_transformation/005.html</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>横型スライド（要確認）</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>未取得</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>MCK04と同じ会議の配布資料。PCから取得する</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MCK-2026-01</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>McKinsey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>新時代の日本へ：躍動と成長に向けた競争力の再構築（白書、2026年10月）</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>mckinsey.com/jp</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.mckinsey.com/jp/</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>未取得</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>報道（EE Times Japan 2026-10-05）で確認。スライド形式か、PDFの所在をPCで確認する</t>
         </is>
       </c>
     </row>
@@ -1962,7 +2142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:O115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6966,6 +7146,1977 @@
       <c r="O88" t="inlineStr">
         <is>
           <t>課題と解決の間に原因を1段挟み、なぜその解決かを読ませる</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>3</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>目次（題のみ）</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>目次の再掲</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>今の節だけ塗りの帯に白文字</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>目次を章扉に再掲し、今の節だけ反転。細目も同じ字下げで残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>4</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>4</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>新型候補</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>題のみ</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2・左右</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>対象・対象外の2列</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>✓と×の丸印、右列は淡い面</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>調査の範囲を「当てはまる／当てはまらない」で最初に約束する</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>6</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>6</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>P70</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2・左右</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>シナリオのカード</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>主軸のシナリオだけ淡い青の面</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>本資料の主軸（p.9-19）</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>出典行のみ</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>2つのシナリオを同じ項目の並びでカードにし、主軸だけ面で示す</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>7</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>7</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>P80</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>題（参考）</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>排出削減のコストカーブ</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>番号付きの注記箱で読み方を説明</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>番号付きの吹き出し6つ</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>出典行</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>幅＝量・高さ＝単価のコストカーブの読み方を、番号付きの注記で1枚にまとめる</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>9</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>9</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>P54</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2・左右（図＋帯）</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2期間の棒</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>右3分の1のグレーの帯に太字の一文＋箇条</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>棒の下に排出削減量の丸の印</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>注1つ・出典行</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>左に図、右3分の1の帯に「太字の一文＋箇条」を2段</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>10</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>10</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>P79</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>行列（行＝論点、列＝日本・EU）</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>小さな棒の推移</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>差の%を棒の上に太字</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>行の見出しに読み取りの文を置き、日本とEUの小さな棒を同じ縮尺で並べる</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>11</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>11</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>P79</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>行列（行＝部門、列＝日本・欧州＋説明）</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>対向の横棒</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>出典行</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>部門をアイコン＋名前で行見出しにし、日欧の値と共通点・相違点を並べる</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>12</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>12</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>P79</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>行列（行＝部門、列＝日本・欧州＋背景）</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>基準線をはさむ横棒</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>水色と濃紺の2色</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>注1つ</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>注・出典行</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>基準線の左右に棒を描き、右列で行ごとの背景を説明する</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>13</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>13</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>結論文1行（参考）</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2・上下（日本・EU）</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>ウォーターフォール</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>要因の下に全体に占める割合を黒い丸の印</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>肩番号の注4つ</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>注・出典行</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>要因の下に割合の丸の印を並べ、効いている要因を数字で示す</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>15</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>15</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>P80</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>コストカーブ</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>部門を色で塗り分け、平均線に「Ø -34」</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>引き出し線のラベル</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>注・出典行</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>コストカーブで0より下と上を分け、平均の線に値を付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>16</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>16</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>P80</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>コストカーブ</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>引き出し線のラベル</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>注・出典行</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>2030年版（p.15）と2050年版を同じ縮尺で並べ、単価の上がり方を比べる</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>17</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>17</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2・上下＋右の帯</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2つのウォーターフォール</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>右の帯に太字の見出し＋本文の2段</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>平均削減コストを楕円の印で</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>出典行</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>同じ要因の並びのウォーターフォールを縦に重ね、右の帯で業界ごとに読み取る</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>20</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>20</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>P35</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>題のみ</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2・左右</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>番号付きの論点2つ</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>番号の丸印</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>論点を①ミクロ②マクロの2列で示し、以降のページに番号を持ち込む</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>22</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>22</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2・左右</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>ウォーターフォールと棒</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>増分シェアの丸の印</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>出典行</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>左に地域別の増分の積上げ、右に対GDP比の棒で2方向から示す</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>23</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>23</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2・左右</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>バブル散布図と100%積上げ</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>日本だけ水色</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>出典行</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>左に散布バブル、右に構成比の2本の100%積上げを置き、日本の小ささを2方向から示す</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>24</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>24</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2・上下</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>事例の積上げ棒と線</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>転機に吹き出し</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>肩番号の注</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>注・出典行</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>企業事例の転換を設備量と利益の2段で示す（色が多い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>26</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>26</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>P27</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2・上下＋右の帯</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2シナリオの棒</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>差を括弧と%で</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>2つのシナリオの差を括弧と「−17%」で示し、右の帯で理由を説明する</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>27</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>27</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>P33</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>3・上下＋右の帯</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>同じ横位置の積上げ棒</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>差を括弧と%で</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>出典行</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>3つの指標を同じ横位置で縦に並べ、右の帯に段ごとの読み取りを置く</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>28</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>28</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>4列</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>アイコン＋見出し＋本文</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>重要語を太字</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>出典行</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>4つの打ち手をアイコン付きの列にし、見出しの下に細線</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>30</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>30</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>P41</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2・左右（図＋帯）</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>積上げ縦棒</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>合計を棒の上の濃い丸の印で</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>肩番号の注</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>注・出典行</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>合計を丸の印で示し、右の帯にアイコン付きの累計の内訳表（値と%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>31</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>31</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>P73</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>結論文3行</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2・左右（図＋帯）</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>増減の積上げ棒</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>平均線に「Ø -14」</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>肩番号の注</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>注・出典行</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>基準線の上下に増減を積み、平均の線と右の内訳表で全体を示す</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>32</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>MCK04</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>32</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>新型候補</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>結論文3行</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2＋右の帯</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>面グラフ2つ</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>右の帯に大きな数字3つ</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>注4つ</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>注・出典行</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>面グラフの下に割合の行、右の帯に時点ごとの要点を大きな数字で</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>4</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>MCK05</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>4</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>P31</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>3×3のマス</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>マスの中の大きな数字</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>赤・水色の大きな数字（採らない）</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>条件×シナリオの3×3のマスに大きな数字を置き、下に合計の帯</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>5</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>MCK05</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>5</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>P27</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>題1行</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>3・左右</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>シナリオ別の小さな積上げ棒</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>注記の吹き出し1つ</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>肩番号の注2つ</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>注・出典行</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>3シナリオの小図を横に並べ、下に前提（達成時期）の行をそろえる（背景色は採らない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>6</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>MCK05</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>6</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>P27</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>題1行</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1＋右の帯</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>範囲の帯（2本）</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>右の帯に太字の一文</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>肩番号の注</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>注・出典行</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>値の幅を帯で示し、交差する点を右の帯で読み取る</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>7</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>MCK05</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>7</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>結論文2行</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1＋右の帯</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>学習曲線（対数軸）</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>注3つ</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>注・出典行</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>技術ごとのコスト低下を対数軸の散布図で比べる</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>9</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>MCK05</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>9</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>P38</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>題1行</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2・左右</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>積上げ縦棒</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>「~50%」を大きな数字で棒の横に</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>注1つ</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>注・出典行</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>構成の棒の横に、言いたい割合だけを大きな数字で置く</t>
         </is>
       </c>
     </row>
